--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5278-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5278-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{345F6197-3E34-4C3E-B801-9B1267044892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D437A657-A931-4843-B966-1F440F450866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E69F35CF-A53B-4C65-8E14-D72024912EAC}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{A62E74CF-8DAB-4944-A5BA-4C4BE1F0DF93}"/>
   </bookViews>
   <sheets>
     <sheet name="5278-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1618,23 +1618,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C18157-746B-4FFE-B0FC-30A1A2EB18D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7317DCA-EB96-4BC8-8EC6-14CFA1C4E38A}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="7" width="8.21875" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.21875" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1692,7 +1692,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1788,7 +1788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1868,7 +1868,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>7.93</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="49">
         <v>2019</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>27</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="51">
         <v>2018</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="49">
         <v>2017</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2016</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="49">
         <v>2015</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="51">
         <v>2014</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>6.63</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="49">
         <v>2013</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="51" t="s">
         <v>77</v>
       </c>
